--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2505-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2505-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4539924A-72A5-41C6-9935-400B83DD1F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8FB0046F-94B9-4836-98E6-7C65102E04AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{5BCD88AD-4B5C-40F9-B894-CDA6CA40C808}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{E9D3D067-634A-4AF5-BC32-B081C32204AF}"/>
   </bookViews>
   <sheets>
     <sheet name="2505-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1496,30 +1496,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF0FA92F-9C52-46D1-815F-5FDDAADDC127}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22558E51-D7B7-4409-8198-C99080C2EA69}">
   <dimension ref="A1:X49"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1553,7 +1553,7 @@
       <c r="W1" s="29"/>
       <c r="X1" s="21"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1589,7 +1589,7 @@
       <c r="W2" s="31"/>
       <c r="X2" s="32"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="X3" s="35"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1709,7 +1709,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="36">
         <v>2024</v>
       </c>
@@ -1781,7 +1781,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="38">
         <v>2023</v>
       </c>
@@ -1853,7 +1853,7 @@
         <v>1.94</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="36">
         <v>2022</v>
       </c>
@@ -1925,7 +1925,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="38">
         <v>2021</v>
       </c>
@@ -1997,7 +1997,7 @@
         <v>5.08</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="15" t="s">
         <v>30</v>
       </c>
@@ -2071,7 +2071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="15" t="s">
         <v>30</v>
       </c>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="15" t="s">
         <v>30</v>
       </c>
@@ -2219,7 +2219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="15" t="s">
         <v>30</v>
       </c>
@@ -2293,7 +2293,7 @@
         <v>2.9</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="15" t="s">
         <v>30</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>2.1800000000000002</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="36">
         <v>2020</v>
       </c>
@@ -2439,7 +2439,7 @@
         <v>16.899999999999999</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>30</v>
       </c>
@@ -2513,7 +2513,7 @@
         <v>4.37</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="11" t="s">
         <v>30</v>
       </c>
@@ -2587,7 +2587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>30</v>
       </c>
@@ -2661,7 +2661,7 @@
         <v>12.5</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="38">
         <v>2019</v>
       </c>
@@ -2733,7 +2733,7 @@
         <v>1.25</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="36">
         <v>2018</v>
       </c>
@@ -2805,7 +2805,7 @@
         <v>4.42</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="38">
         <v>2017</v>
       </c>
@@ -2877,7 +2877,7 @@
         <v>2.38</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="36">
         <v>2016</v>
       </c>
@@ -2949,7 +2949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="38">
         <v>2015</v>
       </c>
@@ -3021,7 +3021,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="36">
         <v>2014</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>1.1100000000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="38">
         <v>2013</v>
       </c>
@@ -3165,7 +3165,7 @@
         <v>3.24</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="36">
         <v>2012</v>
       </c>
@@ -3237,7 +3237,7 @@
         <v>8.14</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="38">
         <v>2011</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="36">
         <v>2010</v>
       </c>
@@ -3381,7 +3381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="38">
         <v>2009</v>
       </c>
@@ -3453,7 +3453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="36">
         <v>2008</v>
       </c>
@@ -3525,7 +3525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="38">
         <v>2007</v>
       </c>
@@ -3597,7 +3597,7 @@
         <v>4.49</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="36">
         <v>2006</v>
       </c>
@@ -3669,7 +3669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="38">
         <v>2005</v>
       </c>
@@ -3741,7 +3741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="36">
         <v>2004</v>
       </c>
@@ -3813,7 +3813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="38">
         <v>2003</v>
       </c>
@@ -3885,7 +3885,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="36">
         <v>2002</v>
       </c>
@@ -3957,7 +3957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="38">
         <v>2001</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="36">
         <v>2000</v>
       </c>
@@ -4101,7 +4101,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="38">
         <v>1999</v>
       </c>
@@ -4173,7 +4173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="36">
         <v>1998</v>
       </c>
@@ -4245,7 +4245,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="38">
         <v>1997</v>
       </c>
@@ -4317,7 +4317,7 @@
         <v>23.5</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="36">
         <v>1996</v>
       </c>
@@ -4389,7 +4389,7 @@
         <v>5.37</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="38">
         <v>1995</v>
       </c>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="36">
         <v>1994</v>
       </c>
@@ -4533,7 +4533,7 @@
         <v>5.56</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="38">
         <v>1993</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="36">
         <v>1992</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="38">
         <v>1991</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="36">
         <v>1990</v>
       </c>
@@ -4821,7 +4821,7 @@
         <v>2.88</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="13" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="13" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="38">
         <v>1989</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="36" t="s">
         <v>52</v>
       </c>
